--- a/files/九龙-何文田-泓璟.xlsx
+++ b/files/九龙-何文田-泓璟.xlsx
@@ -17,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="19">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0"/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,6 +116,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -200,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -212,6 +219,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -256,13 +266,16 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,7 +652,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -754,23 +767,19 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>5481000</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -779,12 +788,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -794,7 +803,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -824,23 +833,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>7344000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -849,12 +854,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -864,7 +869,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -894,23 +899,19 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>6642000</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -919,12 +920,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -934,7 +935,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -964,23 +965,19 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -989,12 +986,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1004,7 +1001,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1034,23 +1031,19 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5481000</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1059,12 +1052,12 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1074,7 +1067,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1104,23 +1097,19 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>7344000</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1129,12 +1118,12 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1144,7 +1133,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1174,23 +1163,19 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6642000</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1199,12 +1184,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1214,7 +1199,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1244,23 +1229,19 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6750000</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1269,12 +1250,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1284,7 +1265,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4954,23 +4935,19 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H63" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="n">
+        <v>5618000</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>23119</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4979,12 +4956,12 @@
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
@@ -4994,7 +4971,7 @@
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5024,23 +5001,19 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>3828000</v>
+      </c>
+      <c r="I64" s="5" t="n">
+        <v>22786</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -5049,12 +5022,12 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
@@ -5064,7 +5037,7 @@
       </c>
       <c r="N64" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5094,23 +5067,19 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>4180000</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>23750</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -5119,12 +5088,12 @@
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -5134,7 +5103,7 @@
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6074,23 +6043,19 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>3678000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>21893</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -6099,12 +6064,12 @@
       </c>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -6114,7 +6079,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7125,115 +7090,195 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>泓璟 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>楼层</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
     </row>
     <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 250呎 (开放式)
+$675万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 246呎 (1房)
+$664万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 272呎 (1房)
+$734万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 203呎 (开放式)
+$548万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 250呎 (开放式)
+$675万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 246呎 (1房)
+$664万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 272呎 (1房)
+$734万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 203呎 (开放式)
+$548万
+$27,000/呎
+(26年-09月-01日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
 招标单位
@@ -7241,7 +7286,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>B | 246呎 (1房)
 招标单位
@@ -7249,7 +7294,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D5" s="19" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>C | 272呎 (1房)
 招标单位
@@ -7257,8 +7302,8 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr"/>
-      <c r="F5" s="19" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 203呎 (开放式)
 招标单位
@@ -7267,509 +7312,476 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 250呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>B | 246呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 272呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr"/>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 203呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+$562万
+$23,119/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>B | 246呎 (1房)
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>C | 272呎 (1房)
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="19" t="inlineStr">
-        <is>
-          <t>E | 203呎 (开放式)
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>A | 250呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>B | 246呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>C | 272呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="19" t="inlineStr">
-        <is>
-          <t>E | 203呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>A | 250呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>B | 246呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t>C | 272呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t>E | 203呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 招标单位
@@ -7777,7 +7789,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 招标单位
@@ -7785,7 +7797,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 招标单位
@@ -7793,7 +7805,101 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E17" s="19" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+$418万
+$23,750/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+$383万
+$22,786/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 176呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 168呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 243呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 224呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 174呎 (开放式)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 招标单位
@@ -7801,7 +7907,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
 招标单位
@@ -7810,13 +7916,13 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 招标单位
@@ -7824,7 +7930,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 224呎 (开放式)
 招标单位
@@ -7832,7 +7938,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D18" s="19" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 招标单位
@@ -7840,7 +7946,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 招标单位
@@ -7848,69 +7954,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
+$368万
+$21,893/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 243呎 (开放式)
 招标单位
@@ -7918,15 +7977,15 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 187呎 (开放式)
 招标单位
 -
 (在售)</t>
         </is>
       </c>
-      <c r="D20" s="19" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 174呎 (开放式)
 招标单位
@@ -7934,7 +7993,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E20" s="19" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 176呎 (开放式)
 招标单位
@@ -7942,101 +8001,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 224呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 168呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 243呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 187呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 174呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 176呎 (开放式)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 130呎 (开放式)
 招标单位
@@ -8046,12 +8011,12 @@
       </c>
     </row>
     <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 206呎 (开放式)
 -
@@ -8059,7 +8024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="21" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 221呎 (开放式)
 -
@@ -8067,7 +8032,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 144呎 (开放式)
 -
@@ -8075,7 +8040,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="21" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 146呎 (开放式)
 -
@@ -8083,7 +8048,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 165呎 (开放式)
 -
